--- a/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T1791L_W0035F0001T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.40213418811378</v>
+        <v>14.36534680556849</v>
       </c>
       <c r="D2" t="n">
-        <v>1.750495961466667</v>
+        <v>0.2844555937383334</v>
       </c>
       <c r="E2" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F2" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>95.78141565654313</v>
+        <v>15.56448004418826</v>
       </c>
       <c r="D3" t="n">
-        <v>13.25018198104706</v>
+        <v>2.153154571920147</v>
       </c>
       <c r="E3" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F3" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.41282731604693</v>
+        <v>2.342084438857626</v>
       </c>
       <c r="D4" t="n">
-        <v>7.670026151908801</v>
+        <v>1.24637924968518</v>
       </c>
       <c r="E4" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F4" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>56.44560029011387</v>
+        <v>9.172410047143504</v>
       </c>
       <c r="D5" t="n">
-        <v>50.61546597086242</v>
+        <v>8.225013220265144</v>
       </c>
       <c r="E5" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F5" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.97543321054947</v>
+        <v>4.708507896714289</v>
       </c>
       <c r="D6" t="n">
-        <v>30.56758109049556</v>
+        <v>4.967231927205529</v>
       </c>
       <c r="E6" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F6" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>69.30525424777487</v>
+        <v>11.26210381526342</v>
       </c>
       <c r="D7" t="n">
-        <v>33.41253611213079</v>
+        <v>5.429537118221254</v>
       </c>
       <c r="E7" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F7" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>68.38548923848268</v>
+        <v>11.11264200125344</v>
       </c>
       <c r="D8" t="n">
-        <v>27.96690132003266</v>
+        <v>4.544621464505307</v>
       </c>
       <c r="E8" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F8" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>50.77552695197203</v>
+        <v>8.251023129695454</v>
       </c>
       <c r="D9" t="n">
-        <v>48.9841968016688</v>
+        <v>7.959931980271181</v>
       </c>
       <c r="E9" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F9" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>37.8305167303269</v>
+        <v>6.147458968678121</v>
       </c>
       <c r="D10" t="n">
-        <v>35.96461822962643</v>
+        <v>5.844250462314295</v>
       </c>
       <c r="E10" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F10" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>64.99416260820477</v>
+        <v>10.56155142383328</v>
       </c>
       <c r="D11" t="n">
-        <v>26.75003245065529</v>
+        <v>4.346880273231484</v>
       </c>
       <c r="E11" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F11" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>95.05908788771733</v>
+        <v>15.44710178175407</v>
       </c>
       <c r="D12" t="n">
-        <v>23.88423041237883</v>
+        <v>3.88118744201156</v>
       </c>
       <c r="E12" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F12" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>56.21943245412603</v>
+        <v>9.135657773795479</v>
       </c>
       <c r="D13" t="n">
-        <v>46.50069070574233</v>
+        <v>7.556362239683128</v>
       </c>
       <c r="E13" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F13" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>11.73819118822954</v>
+        <v>1.9074560680873</v>
       </c>
       <c r="D14" t="n">
-        <v>14.56341514755405</v>
+        <v>2.366554961477534</v>
       </c>
       <c r="E14" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F14" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>80.44916154934765</v>
+        <v>13.07298875176899</v>
       </c>
       <c r="D15" t="n">
-        <v>13.0553278646373</v>
+        <v>2.12149077800356</v>
       </c>
       <c r="E15" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F15" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>57.02126712590525</v>
+        <v>9.265955907959604</v>
       </c>
       <c r="D16" t="n">
-        <v>37.35308570414652</v>
+        <v>6.06987642692381</v>
       </c>
       <c r="E16" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F16" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>6.781512012409476</v>
+        <v>1.10199570201654</v>
       </c>
       <c r="D17" t="n">
-        <v>2.84550837808457</v>
+        <v>0.4623951114387427</v>
       </c>
       <c r="E17" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F17" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>49.04730932354097</v>
+        <v>7.970187765075408</v>
       </c>
       <c r="D18" t="n">
-        <v>45.11909783384444</v>
+        <v>7.331853397999721</v>
       </c>
       <c r="E18" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F18" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>67.96166050949087</v>
+        <v>11.04376983279227</v>
       </c>
       <c r="D19" t="n">
-        <v>19.34959501532124</v>
+        <v>3.144309189989702</v>
       </c>
       <c r="E19" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F19" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>10.61174876755165</v>
+        <v>1.724409174727144</v>
       </c>
       <c r="D20" t="n">
-        <v>4.763789921326152</v>
+        <v>0.7741158622154998</v>
       </c>
       <c r="E20" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F20" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>71.82420023016327</v>
+        <v>11.67143253740153</v>
       </c>
       <c r="D21" t="n">
-        <v>28.97379683054634</v>
+        <v>4.708241984963781</v>
       </c>
       <c r="E21" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F21" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>17.91626194040012</v>
+        <v>2.911392565315019</v>
       </c>
       <c r="D22" t="n">
-        <v>9.911510470691679</v>
+        <v>1.610620451487398</v>
       </c>
       <c r="E22" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F22" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>41.40104902469931</v>
+        <v>6.727670466513638</v>
       </c>
       <c r="D23" t="n">
-        <v>36.6148333179046</v>
+        <v>5.949910414159499</v>
       </c>
       <c r="E23" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F23" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>17.68485016702456</v>
+        <v>2.873788152141491</v>
       </c>
       <c r="D24" t="n">
-        <v>5.439837932759933</v>
+        <v>0.8839736640734892</v>
       </c>
       <c r="E24" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F24" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>58.9904237682689</v>
+        <v>9.585943862343697</v>
       </c>
       <c r="D25" t="n">
-        <v>33.01046117599925</v>
+        <v>5.364199941099878</v>
       </c>
       <c r="E25" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F25" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>84.35224512362805</v>
+        <v>13.70723983258956</v>
       </c>
       <c r="D26" t="n">
-        <v>44.11642189202967</v>
+        <v>7.168918557454822</v>
       </c>
       <c r="E26" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F26" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>48.51361305781432</v>
+        <v>7.883462121894827</v>
       </c>
       <c r="D27" t="n">
-        <v>39.44192715677409</v>
+        <v>6.40931316297579</v>
       </c>
       <c r="E27" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F27" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>78.27572088824684</v>
+        <v>12.71980464434011</v>
       </c>
       <c r="D28" t="n">
-        <v>40.18347606278423</v>
+        <v>6.529814860202437</v>
       </c>
       <c r="E28" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F28" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1344,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>3.920938681088064</v>
+        <v>0.6371525356768104</v>
       </c>
       <c r="D29" t="n">
-        <v>11.3510266050548</v>
+        <v>1.844541823321405</v>
       </c>
       <c r="E29" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F29" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1376,16 +1376,16 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>41.02249917477734</v>
+        <v>6.666156115901318</v>
       </c>
       <c r="D30" t="n">
-        <v>40.62562294151341</v>
+        <v>6.601663727995929</v>
       </c>
       <c r="E30" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F30" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1408,16 +1408,16 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>60.70214440906501</v>
+        <v>9.864098466473065</v>
       </c>
       <c r="D31" t="n">
-        <v>47.98026576393441</v>
+        <v>7.796793186639342</v>
       </c>
       <c r="E31" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F31" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>8.912286831088034</v>
+        <v>1.448246610051806</v>
       </c>
       <c r="D32" t="n">
-        <v>21.26406578778291</v>
+        <v>3.455410690514723</v>
       </c>
       <c r="E32" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F32" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>73.60791049896335</v>
+        <v>11.96128545608154</v>
       </c>
       <c r="D33" t="n">
-        <v>50.79882051285376</v>
+        <v>8.254808333338737</v>
       </c>
       <c r="E33" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F33" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1504,16 +1504,16 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>18.10230149371903</v>
+        <v>2.941623992729343</v>
       </c>
       <c r="D34" t="n">
-        <v>0.675862503366474</v>
+        <v>0.109827656797052</v>
       </c>
       <c r="E34" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F34" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1536,16 +1536,16 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>17.90099428865588</v>
+        <v>2.908911571906581</v>
       </c>
       <c r="D35" t="n">
-        <v>17.58233264701575</v>
+        <v>2.85712905514006</v>
       </c>
       <c r="E35" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F35" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1568,16 +1568,16 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>19.83753068381559</v>
+        <v>3.223598736120033</v>
       </c>
       <c r="D36" t="n">
-        <v>31.11868420689667</v>
+        <v>5.056786183620709</v>
       </c>
       <c r="E36" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F36" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1600,16 +1600,16 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>47.50517208240134</v>
+        <v>7.719590463390218</v>
       </c>
       <c r="D37" t="n">
-        <v>47.12666239961602</v>
+        <v>7.658082639937603</v>
       </c>
       <c r="E37" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F37" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1632,16 +1632,16 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>28.76480370948075</v>
+        <v>4.674280602790622</v>
       </c>
       <c r="D38" t="n">
-        <v>28.90027391627313</v>
+        <v>4.696294511394383</v>
       </c>
       <c r="E38" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F38" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1664,16 +1664,16 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>57.02109394061479</v>
+        <v>9.265927765349904</v>
       </c>
       <c r="D39" t="n">
-        <v>56.68741262521512</v>
+        <v>9.211704551597457</v>
       </c>
       <c r="E39" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F39" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1696,16 +1696,16 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>15.72593715284416</v>
+        <v>2.555464787337175</v>
       </c>
       <c r="D40" t="n">
-        <v>11.30594178630935</v>
+        <v>1.837215540275269</v>
       </c>
       <c r="E40" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F40" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1728,16 +1728,16 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>64.57019226465839</v>
+        <v>10.49265624300699</v>
       </c>
       <c r="D41" t="n">
-        <v>63.192937891638</v>
+        <v>10.26885240739117</v>
       </c>
       <c r="E41" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F41" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1760,16 +1760,16 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>22.23154355270668</v>
+        <v>3.612625827314835</v>
       </c>
       <c r="D42" t="n">
-        <v>23.58541084946944</v>
+        <v>3.832629263038785</v>
       </c>
       <c r="E42" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F42" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1792,16 +1792,16 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>12.34707802919311</v>
+        <v>2.00640017974388</v>
       </c>
       <c r="D43" t="n">
-        <v>12.48259159707967</v>
+        <v>2.028421134525447</v>
       </c>
       <c r="E43" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F43" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1824,16 +1824,16 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>50.94346632751939</v>
+        <v>8.278313278221901</v>
       </c>
       <c r="D44" t="n">
-        <v>50.63631394560377</v>
+        <v>8.228401016160612</v>
       </c>
       <c r="E44" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F44" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1856,16 +1856,16 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>29.37915694630112</v>
+        <v>4.774113003773933</v>
       </c>
       <c r="D45" t="n">
-        <v>18.82555751119677</v>
+        <v>3.059153095569475</v>
       </c>
       <c r="E45" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F45" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1888,16 +1888,16 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>27.44474675510536</v>
+        <v>4.459771347704621</v>
       </c>
       <c r="D46" t="n">
-        <v>33.93901619607987</v>
+        <v>5.515090131862979</v>
       </c>
       <c r="E46" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F46" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1920,16 +1920,16 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>49.17010102764782</v>
+        <v>7.99014141699277</v>
       </c>
       <c r="D47" t="n">
-        <v>48.90581969493007</v>
+        <v>7.947195700426137</v>
       </c>
       <c r="E47" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F47" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1952,16 +1952,16 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>59.35991997039886</v>
+        <v>9.645986995189816</v>
       </c>
       <c r="D48" t="n">
-        <v>59.10418911847115</v>
+        <v>9.604430731751561</v>
       </c>
       <c r="E48" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F48" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1984,16 +1984,16 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>34.97565760860869</v>
+        <v>5.683544361398911</v>
       </c>
       <c r="D49" t="n">
-        <v>31.74454361591478</v>
+        <v>5.158488337586151</v>
       </c>
       <c r="E49" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F49" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2016,16 +2016,16 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>23.17926098835785</v>
+        <v>3.76662991060815</v>
       </c>
       <c r="D50" t="n">
-        <v>23.54018030539981</v>
+        <v>3.82527929962747</v>
       </c>
       <c r="E50" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F50" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2048,16 +2048,16 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>38.30395957821466</v>
+        <v>6.224393431459882</v>
       </c>
       <c r="D51" t="n">
-        <v>37.59572145344384</v>
+        <v>6.109304736184625</v>
       </c>
       <c r="E51" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F51" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2080,16 +2080,16 @@
         <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>43.58225065263334</v>
+        <v>7.082115731052919</v>
       </c>
       <c r="D52" t="n">
-        <v>36.85380288956405</v>
+        <v>5.988742969554158</v>
       </c>
       <c r="E52" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F52" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2112,16 +2112,16 @@
         <v>52</v>
       </c>
       <c r="C53" t="n">
-        <v>56.44041388988207</v>
+        <v>9.171567257105837</v>
       </c>
       <c r="D53" t="n">
-        <v>56.2460323950032</v>
+        <v>9.13998026418802</v>
       </c>
       <c r="E53" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F53" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2144,16 +2144,16 @@
         <v>53</v>
       </c>
       <c r="C54" t="n">
-        <v>67.83851705256076</v>
+        <v>11.02375902104112</v>
       </c>
       <c r="D54" t="n">
-        <v>67.64233335269435</v>
+        <v>10.99187916981283</v>
       </c>
       <c r="E54" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F54" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2176,16 +2176,16 @@
         <v>54</v>
       </c>
       <c r="C55" t="n">
-        <v>51.9917527612041</v>
+        <v>8.448659823695667</v>
       </c>
       <c r="D55" t="n">
-        <v>42.98506774896041</v>
+        <v>6.985073509206067</v>
       </c>
       <c r="E55" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F55" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2208,16 +2208,16 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>50.21088506013447</v>
+        <v>8.159268822271851</v>
       </c>
       <c r="D56" t="n">
-        <v>46.52091794541933</v>
+        <v>7.559649166130641</v>
       </c>
       <c r="E56" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F56" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2240,16 +2240,16 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>54.73406172683457</v>
+        <v>8.894285030610618</v>
       </c>
       <c r="D57" t="n">
-        <v>54.59784101304285</v>
+        <v>8.872149164619463</v>
       </c>
       <c r="E57" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F57" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2272,16 +2272,16 @@
         <v>57</v>
       </c>
       <c r="C58" t="n">
-        <v>79.82799635786142</v>
+        <v>12.97204940815248</v>
       </c>
       <c r="D58" t="n">
-        <v>79.64121170277123</v>
+        <v>12.94169690170033</v>
       </c>
       <c r="E58" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F58" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2304,16 +2304,16 @@
         <v>58</v>
       </c>
       <c r="C59" t="n">
-        <v>67.92603152797646</v>
+        <v>11.03798012329618</v>
       </c>
       <c r="D59" t="n">
-        <v>67.81614161873982</v>
+        <v>11.02012301304522</v>
       </c>
       <c r="E59" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F59" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2336,16 +2336,16 @@
         <v>59</v>
       </c>
       <c r="C60" t="n">
-        <v>62.24524701333833</v>
+        <v>10.11485263966748</v>
       </c>
       <c r="D60" t="n">
-        <v>51.96668567219856</v>
+        <v>8.444586421732266</v>
       </c>
       <c r="E60" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F60" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2368,16 +2368,16 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>56.63017497911744</v>
+        <v>9.202403434106584</v>
       </c>
       <c r="D61" t="n">
-        <v>56.57009757875353</v>
+        <v>9.192640856547449</v>
       </c>
       <c r="E61" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F61" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2400,16 +2400,16 @@
         <v>61</v>
       </c>
       <c r="C62" t="n">
-        <v>82.66594382089599</v>
+        <v>13.4332158708956</v>
       </c>
       <c r="D62" t="n">
-        <v>82.523163591173</v>
+        <v>13.41001408356561</v>
       </c>
       <c r="E62" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F62" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
         <v>62</v>
       </c>
       <c r="C63" t="n">
-        <v>63.42460929091676</v>
+        <v>10.30649900977397</v>
       </c>
       <c r="D63" t="n">
-        <v>55.24208067391073</v>
+        <v>8.976838109510494</v>
       </c>
       <c r="E63" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F63" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2464,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="C64" t="n">
-        <v>47.30482246488218</v>
+        <v>7.687033650543354</v>
       </c>
       <c r="D64" t="n">
-        <v>47.69215997584133</v>
+        <v>7.749975996074216</v>
       </c>
       <c r="E64" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F64" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2496,16 +2496,16 @@
         <v>64</v>
       </c>
       <c r="C65" t="n">
-        <v>90.17849331786752</v>
+        <v>14.65400516415347</v>
       </c>
       <c r="D65" t="n">
-        <v>90.07426216805158</v>
+        <v>14.63706760230838</v>
       </c>
       <c r="E65" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F65" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2528,16 +2528,16 @@
         <v>65</v>
       </c>
       <c r="C66" t="n">
-        <v>74.00229024463634</v>
+        <v>12.02537216475341</v>
       </c>
       <c r="D66" t="n">
-        <v>73.96572505564879</v>
+        <v>12.01943032154293</v>
       </c>
       <c r="E66" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F66" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2560,16 +2560,16 @@
         <v>66</v>
       </c>
       <c r="C67" t="n">
-        <v>76.43143621866366</v>
+        <v>12.42010838553285</v>
       </c>
       <c r="D67" t="n">
-        <v>66.68141742391148</v>
+        <v>10.83573033138562</v>
       </c>
       <c r="E67" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F67" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2592,16 +2592,16 @@
         <v>67</v>
       </c>
       <c r="C68" t="n">
-        <v>87.72067872776235</v>
+        <v>14.25461029326138</v>
       </c>
       <c r="D68" t="n">
-        <v>87.6388308691095</v>
+        <v>14.24131001623029</v>
       </c>
       <c r="E68" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F68" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2624,16 +2624,16 @@
         <v>68</v>
       </c>
       <c r="C69" t="n">
-        <v>60.13955185030844</v>
+        <v>9.772677175675121</v>
       </c>
       <c r="D69" t="n">
-        <v>60.53447524958294</v>
+        <v>9.836852228057229</v>
       </c>
       <c r="E69" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F69" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2656,16 +2656,16 @@
         <v>69</v>
       </c>
       <c r="C70" t="n">
-        <v>53.53859487833227</v>
+        <v>8.700021667728993</v>
       </c>
       <c r="D70" t="n">
-        <v>53.91127338629705</v>
+        <v>8.760581925273272</v>
       </c>
       <c r="E70" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F70" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2688,16 +2688,16 @@
         <v>70</v>
       </c>
       <c r="C71" t="n">
-        <v>49.16734844169449</v>
+        <v>7.989694121775354</v>
       </c>
       <c r="D71" t="n">
-        <v>49.48490747332187</v>
+        <v>8.041297464414804</v>
       </c>
       <c r="E71" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F71" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2720,16 +2720,16 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>81.64841653061575</v>
+        <v>13.26786768622506</v>
       </c>
       <c r="D72" t="n">
-        <v>81.62482255985996</v>
+        <v>13.26403366597724</v>
       </c>
       <c r="E72" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F72" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2752,16 +2752,16 @@
         <v>72</v>
       </c>
       <c r="C73" t="n">
-        <v>58.49323373460403</v>
+        <v>9.505150481873155</v>
       </c>
       <c r="D73" t="n">
-        <v>58.82047532896424</v>
+        <v>9.55832724095669</v>
       </c>
       <c r="E73" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F73" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2784,16 +2784,16 @@
         <v>73</v>
       </c>
       <c r="C74" t="n">
-        <v>77.60923670259959</v>
+        <v>12.61150096417243</v>
       </c>
       <c r="D74" t="n">
-        <v>77.60876311721681</v>
+        <v>12.61142400654773</v>
       </c>
       <c r="E74" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F74" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2816,16 +2816,16 @@
         <v>74</v>
       </c>
       <c r="C75" t="n">
-        <v>94.89924922484401</v>
+        <v>15.42112799903715</v>
       </c>
       <c r="D75" t="n">
-        <v>94.83155168855501</v>
+        <v>15.41012714939019</v>
       </c>
       <c r="E75" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F75" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2848,16 +2848,16 @@
         <v>75</v>
       </c>
       <c r="C76" t="n">
-        <v>95.6062386840416</v>
+        <v>15.53601378615676</v>
       </c>
       <c r="D76" t="n">
-        <v>95.57095607219047</v>
+        <v>15.53028036173095</v>
       </c>
       <c r="E76" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F76" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2880,16 +2880,16 @@
         <v>76</v>
       </c>
       <c r="C77" t="n">
-        <v>68.96483595356598</v>
+        <v>11.20678584245447</v>
       </c>
       <c r="D77" t="n">
-        <v>69.13519019062825</v>
+        <v>11.23446840597709</v>
       </c>
       <c r="E77" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F77" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2912,16 +2912,16 @@
         <v>77</v>
       </c>
       <c r="C78" t="n">
-        <v>90.82597079541772</v>
+        <v>14.75922025425538</v>
       </c>
       <c r="D78" t="n">
-        <v>90.83181836988906</v>
+        <v>14.76017048510697</v>
       </c>
       <c r="E78" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F78" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2944,16 +2944,16 @@
         <v>78</v>
       </c>
       <c r="C79" t="n">
-        <v>78.56755835040349</v>
+        <v>12.76722823194057</v>
       </c>
       <c r="D79" t="n">
-        <v>78.95583743746003</v>
+        <v>12.83032358358726</v>
       </c>
       <c r="E79" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F79" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2976,16 +2976,16 @@
         <v>79</v>
       </c>
       <c r="C80" t="n">
-        <v>69.80658806267404</v>
+        <v>11.34357056018453</v>
       </c>
       <c r="D80" t="n">
-        <v>70.13038648080401</v>
+        <v>11.39618780313065</v>
       </c>
       <c r="E80" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F80" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3008,16 +3008,16 @@
         <v>80</v>
       </c>
       <c r="C81" t="n">
-        <v>75.27282306475958</v>
+        <v>12.23183374802343</v>
       </c>
       <c r="D81" t="n">
-        <v>75.45314285040415</v>
+        <v>12.26113571319067</v>
       </c>
       <c r="E81" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F81" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3040,16 +3040,16 @@
         <v>81</v>
       </c>
       <c r="C82" t="n">
-        <v>85.70272542672539</v>
+        <v>13.92669288184288</v>
       </c>
       <c r="D82" t="n">
-        <v>85.77509889506932</v>
+        <v>13.93845357044876</v>
       </c>
       <c r="E82" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F82" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3072,16 +3072,16 @@
         <v>82</v>
       </c>
       <c r="C83" t="n">
-        <v>104.6347386211371</v>
+        <v>17.00314502593478</v>
       </c>
       <c r="D83" t="n">
-        <v>104.6189494033023</v>
+        <v>17.00057927803663</v>
       </c>
       <c r="E83" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F83" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3104,16 +3104,16 @@
         <v>83</v>
       </c>
       <c r="C84" t="n">
-        <v>101.8482637521935</v>
+        <v>16.55034285973145</v>
       </c>
       <c r="D84" t="n">
-        <v>93.49215005012182</v>
+        <v>15.1924743831448</v>
       </c>
       <c r="E84" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F84" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3136,16 +3136,16 @@
         <v>84</v>
       </c>
       <c r="C85" t="n">
-        <v>95.92334051977345</v>
+        <v>15.58754283446319</v>
       </c>
       <c r="D85" t="n">
-        <v>96.31603995458661</v>
+        <v>15.65135649262032</v>
       </c>
       <c r="E85" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F85" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3168,16 +3168,16 @@
         <v>85</v>
       </c>
       <c r="C86" t="n">
-        <v>85.36377763026586</v>
+        <v>13.8716138649182</v>
       </c>
       <c r="D86" t="n">
-        <v>85.73851381387999</v>
+        <v>13.9325084947555</v>
       </c>
       <c r="E86" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F86" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3200,16 +3200,16 @@
         <v>86</v>
       </c>
       <c r="C87" t="n">
-        <v>77.29057171998005</v>
+        <v>12.55971790449676</v>
       </c>
       <c r="D87" t="n">
-        <v>77.5798714390845</v>
+        <v>12.60672910885123</v>
       </c>
       <c r="E87" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F87" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3232,16 +3232,16 @@
         <v>87</v>
       </c>
       <c r="C88" t="n">
-        <v>81.59800184072847</v>
+        <v>13.25967529911838</v>
       </c>
       <c r="D88" t="n">
-        <v>81.73343805730688</v>
+        <v>13.28168368431237</v>
       </c>
       <c r="E88" t="n">
-        <v>25.93121277447987</v>
+        <v>4.213822075852979</v>
       </c>
       <c r="F88" t="n">
-        <v>26.57655514650021</v>
+        <v>4.318690211306284</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
